--- a/outputs_xlsx_solution/test_new4.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_new4.1-wide.xlsx
@@ -59,13 +59,16 @@
     <t>addi X2, X0, 5</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>addi X3, X0, 0</t>
   </si>
   <si>
-    <t>WB/CT</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>addi X4, X0, 4</t>
@@ -83,15 +86,15 @@
     <t>fmul F3, F1, F1</t>
   </si>
   <si>
-    <t>EX</t>
-  </si>
-  <si>
     <t>fadd F2, F2, F3</t>
   </si>
   <si>
     <t>add X1, X1, X4</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>addi X3, X3, 1</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>bne X5, X0, 28</t>
   </si>
   <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
     <t>fsd F2, 200(X0)</t>
   </si>
   <si>
@@ -113,13 +119,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -648,6 +672,30 @@
       <c r="BE1">
         <v>54</v>
       </c>
+      <c r="BF1">
+        <v>55</v>
+      </c>
+      <c r="BG1">
+        <v>56</v>
+      </c>
+      <c r="BH1">
+        <v>57</v>
+      </c>
+      <c r="BI1">
+        <v>58</v>
+      </c>
+      <c r="BJ1">
+        <v>59</v>
+      </c>
+      <c r="BK1">
+        <v>60</v>
+      </c>
+      <c r="BL1">
+        <v>61</v>
+      </c>
+      <c r="BM1">
+        <v>62</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -669,7 +717,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +763,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +774,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -738,7 +786,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +797,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -761,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -772,7 +820,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>5</v>
@@ -784,13 +832,13 @@
         <v>8</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -801,7 +849,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>5</v>
@@ -813,13 +861,13 @@
         <v>8</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -830,7 +878,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -842,16 +890,16 @@
         <v>8</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -871,22 +919,22 @@
         <v>6</v>
       </c>
       <c r="N10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T10" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="U10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -911,8 +959,8 @@
       <c r="P11" t="s">
         <v>10</v>
       </c>
-      <c r="U11" t="s">
-        <v>10</v>
+      <c r="V11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +971,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N12" t="s">
         <v>5</v>
@@ -932,16 +980,16 @@
         <v>6</v>
       </c>
       <c r="P12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
       </c>
-      <c r="U12" t="s">
-        <v>10</v>
+      <c r="W12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -952,7 +1000,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O13" t="s">
         <v>5</v>
@@ -964,13 +1012,13 @@
         <v>8</v>
       </c>
       <c r="R13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S13" t="s">
         <v>10</v>
       </c>
-      <c r="U13" t="s">
-        <v>10</v>
+      <c r="X13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -981,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
         <v>5</v>
@@ -990,16 +1038,16 @@
         <v>6</v>
       </c>
       <c r="R14" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T14" t="s">
         <v>10</v>
       </c>
-      <c r="U14" t="s">
-        <v>10</v>
+      <c r="Y14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1010,7 +1058,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="s">
         <v>5</v>
@@ -1019,13 +1067,16 @@
         <v>6</v>
       </c>
       <c r="S15" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T15" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U15" t="s">
         <v>10</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1036,7 +1087,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U16" t="s">
         <v>5</v>
@@ -1048,16 +1099,16 @@
         <v>8</v>
       </c>
       <c r="X16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1077,22 +1128,22 @@
         <v>6</v>
       </c>
       <c r="X17" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AC17" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1117,8 +1168,8 @@
       <c r="Z18" t="s">
         <v>10</v>
       </c>
-      <c r="AE18" t="s">
-        <v>10</v>
+      <c r="AF18" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1129,7 +1180,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X19" t="s">
         <v>5</v>
@@ -1138,16 +1189,16 @@
         <v>6</v>
       </c>
       <c r="Z19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="s">
         <v>10</v>
       </c>
-      <c r="AE19" t="s">
-        <v>10</v>
+      <c r="AG19" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -1158,7 +1209,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s">
         <v>5</v>
@@ -1170,13 +1221,13 @@
         <v>8</v>
       </c>
       <c r="AB20" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="s">
         <v>10</v>
       </c>
-      <c r="AE20" t="s">
-        <v>10</v>
+      <c r="AH20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1187,7 +1238,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s">
         <v>5</v>
@@ -1196,716 +1247,836 @@
         <v>6</v>
       </c>
       <c r="AB21" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="s">
         <v>10</v>
       </c>
-      <c r="AE21" t="s">
-        <v>10</v>
+      <c r="AI21" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
+      <c r="AA22" t="s">
+        <v>5</v>
       </c>
       <c r="AB22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AD22" t="s">
         <v>8</v>
       </c>
       <c r="AE22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>5</v>
       </c>
       <c r="AC23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD23" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="s">
         <v>8</v>
       </c>
+      <c r="AF23" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>23</v>
+      </c>
       <c r="AL23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>5</v>
       </c>
       <c r="AD24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>23</v>
       </c>
       <c r="AS24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>5</v>
       </c>
       <c r="AE25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>5</v>
       </c>
       <c r="AF26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="s">
         <v>8</v>
       </c>
       <c r="AI26" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AU26" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
       </c>
+      <c r="AF27" t="s">
+        <v>5</v>
+      </c>
       <c r="AG27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS27" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>6</v>
       </c>
       <c r="AI28" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AR28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS28" t="s">
-        <v>16</v>
-      </c>
-      <c r="AT28" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="AW28" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>6</v>
       </c>
       <c r="AJ29" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AW29" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>6</v>
       </c>
       <c r="AK30" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM30" t="s">
         <v>8</v>
       </c>
       <c r="AN30" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ30" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>40</v>
-      </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>6</v>
       </c>
       <c r="AL31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW31" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>23</v>
       </c>
       <c r="AZ31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>6</v>
       </c>
       <c r="AM32" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ32" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BA32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>6</v>
       </c>
       <c r="AN33" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AO33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AQ33" t="s">
-        <v>16</v>
-      </c>
-      <c r="AR33" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ33" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BB33" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>19</v>
       </c>
       <c r="AP34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ34" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR34" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AT34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AW34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ34" t="s">
-        <v>16</v>
-      </c>
-      <c r="BA34" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BC34" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>19</v>
       </c>
       <c r="AQ35" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR35" t="s">
-        <v>6</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA35" t="s">
-        <v>16</v>
-      </c>
-      <c r="BB35" t="s">
-        <v>16</v>
-      </c>
-      <c r="BC35" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BD35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>19</v>
       </c>
       <c r="AR36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS36" t="s">
-        <v>6</v>
-      </c>
-      <c r="AT36" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD36" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BE36" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS37" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>19</v>
       </c>
       <c r="AT37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU37" t="s">
         <v>8</v>
       </c>
       <c r="AV37" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AW37" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD37" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ37" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA37" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF37" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU38" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV38" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW38" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX38" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>19</v>
+      </c>
+      <c r="BA38" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB38" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC38" t="s">
+        <v>8</v>
       </c>
       <c r="BD38" t="s">
         <v>10</v>
+      </c>
+      <c r="BG38" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>19</v>
       </c>
       <c r="AU39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AW39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY39" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD39" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BH39" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="AS40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>19</v>
       </c>
       <c r="AV40" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW40" t="s">
-        <v>6</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY40" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ40" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD40" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="BI40" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW41" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX41" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ43" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="AZ41" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA41" t="s">
-        <v>6</v>
-      </c>
-      <c r="BB41" t="s">
-        <v>8</v>
-      </c>
-      <c r="BD41" t="s">
-        <v>16</v>
-      </c>
-      <c r="BE41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
+      <c r="AZ44" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA44" t="s">
+        <v>6</v>
+      </c>
+      <c r="BB44" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD44" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM44" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_new4.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_new4.1-wide.xlsx
@@ -107,6 +107,9 @@
     <t>CDB Stall</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fsd F2, 200(X0)</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1773,6 +1779,9 @@
       <c r="AR37" t="s">
         <v>19</v>
       </c>
+      <c r="AS37" t="s">
+        <v>24</v>
+      </c>
       <c r="AT37" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1998,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ44" t="s">
         <v>5</v>
@@ -2012,7 +2021,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
@@ -2020,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -2028,7 +2037,7 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -2036,7 +2045,7 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -2044,7 +2053,7 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2052,7 +2061,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2060,23 +2069,39 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
